--- a/data/trans_orig/IP07C06-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C06-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10580</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17753</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15082</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23641</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21162</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>31805</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24576</t>
+          <t>24324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49057</t>
+          <t>48670</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63534</t>
+          <t>63404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5572</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30103</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41184</t>
+          <t>39834</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43662</t>
+          <t>44077</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66274</t>
+          <t>65980</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33055</t>
+          <t>32398</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51220</t>
+          <t>50583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44988</t>
+          <t>44422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64935</t>
+          <t>65502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89962</t>
+          <t>90736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110712</t>
+          <t>111763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132066</t>
+          <t>132212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>132898</t>
+          <t>133178</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156063</t>
+          <t>155119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>252230</t>
+          <t>251625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281934</t>
+          <t>282313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3962</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13421</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14093</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>12263</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>25520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16120</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>23512</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40160</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28146</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38802</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>60320</t>
+          <t>59422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75860</t>
+          <t>76031</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>10655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28840</t>
+          <t>29049</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46385</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37058</t>
+          <t>36234</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56567</t>
+          <t>56972</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>70051</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>97288</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>51439</t>
+          <t>51222</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73525</t>
+          <t>72891</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38200</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59619</t>
+          <t>58512</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94911</t>
+          <t>95847</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>125630</t>
+          <t>126408</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>170047</t>
+          <t>170079</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>196009</t>
+          <t>196278</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>195584</t>
+          <t>196076</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>221918</t>
+          <t>221481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>371172</t>
+          <t>370811</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>408075</t>
+          <t>408622</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4706</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6062</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12673</t>
+          <t>12408</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22840</t>
+          <t>22385</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22117</t>
+          <t>21800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27250</t>
+          <t>27181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>34054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53918</t>
+          <t>53725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69258</t>
+          <t>69504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>14774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12352</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>24421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>21083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37563</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31518</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49387</t>
+          <t>49231</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56107</t>
+          <t>56287</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80766</t>
+          <t>80993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40231</t>
+          <t>40797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59727</t>
+          <t>60736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32866</t>
+          <t>32759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52385</t>
+          <t>52653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79751</t>
+          <t>78102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105846</t>
+          <t>106887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96704</t>
+          <t>96192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120666</t>
+          <t>118918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115042</t>
+          <t>114443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138842</t>
+          <t>138744</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>220358</t>
+          <t>218033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252973</t>
+          <t>252596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>13981</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12742</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20200</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>18471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>35262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,15%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25805</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>39275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26546</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>39427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57402</t>
+          <t>56459</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73837</t>
+          <t>74221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32413</t>
+          <t>32373</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55820</t>
+          <t>56263</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65195</t>
+          <t>65796</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>85494</t>
+          <t>84654</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>116026</t>
+          <t>114939</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>61425</t>
+          <t>61969</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85615</t>
+          <t>86353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73248</t>
+          <t>73308</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117099</t>
+          <t>117436</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>150878</t>
+          <t>151131</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159391</t>
+          <t>158722</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>188221</t>
+          <t>187007</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>174505</t>
+          <t>173440</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203625</t>
+          <t>203531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>342251</t>
+          <t>342725</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384527</t>
+          <t>383667</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3382</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>783</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>18406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11017</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>21003</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,89%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>11873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>24663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16724</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18820</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>35528</t>
+          <t>35639</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>21319</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38790</t>
+          <t>38626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27312</t>
+          <t>27282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46504</t>
+          <t>45518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53423</t>
+          <t>53570</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78022</t>
+          <t>79346</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39432</t>
+          <t>40216</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60784</t>
+          <t>60483</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67716</t>
+          <t>67927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91754</t>
+          <t>91922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121222</t>
+          <t>122436</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129897</t>
+          <t>128107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>154138</t>
+          <t>154338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118270</t>
+          <t>117931</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144475</t>
+          <t>144726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254983</t>
+          <t>254380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291912</t>
+          <t>291027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,58%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20042</t>
+          <t>19266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19977</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26141</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25271</t>
+          <t>25437</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41767</t>
+          <t>43015</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36520</t>
+          <t>36652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49646</t>
+          <t>50101</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40299</t>
+          <t>40090</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53699</t>
+          <t>54187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81207</t>
+          <t>80966</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100017</t>
+          <t>100037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,51%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22233</t>
+          <t>21955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>35233</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25669</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33705</t>
+          <t>34161</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>54815</t>
+          <t>55873</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>32009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51946</t>
+          <t>52980</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33714</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>54533</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>70702</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>99276</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>55379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>80223</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>76168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>104155</t>
+          <t>102962</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>139592</t>
+          <t>137332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>176228</t>
+          <t>174457</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>184767</t>
+          <t>186369</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>214667</t>
+          <t>216364</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>177055</t>
+          <t>176833</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>210486</t>
+          <t>207611</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>374696</t>
+          <t>370732</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>415294</t>
+          <t>415043</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,88%</t>
         </is>
       </c>
     </row>
